--- a/output/pdf_financials_xlsx/LION.xlsx
+++ b/output/pdf_financials_xlsx/LION.xlsx
@@ -2195,13 +2195,13 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>1.619201</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>1.619201</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>1.619201</v>
       </c>
       <c r="E92" s="3" t="n">
         <v>0</v>
@@ -4060,7 +4060,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E30" t="inlineStr">
         <is>
           <t>-</t>
@@ -4194,7 +4198,11 @@
           <t>Share-based payment reserve (Note 7)</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr"/>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E34" s="5" t="n">
         <v>1.619201</v>
       </c>

--- a/output/pdf_financials_xlsx/LION.xlsx
+++ b/output/pdf_financials_xlsx/LION.xlsx
@@ -639,16 +639,16 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.000249</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.000621</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.005747</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.000851</v>
       </c>
     </row>
     <row r="13">
@@ -946,16 +946,16 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-1.514531</v>
+        <v>-1.51478</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.451042</v>
+        <v>-0.451663</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.356121</v>
+        <v>-0.361868</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.360083</v>
+        <v>-0.360934</v>
       </c>
     </row>
     <row r="28">
@@ -984,16 +984,16 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-1.514531</v>
+        <v>-1.51478</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.451042</v>
+        <v>-0.451663</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.356121</v>
+        <v>-0.361868</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.360083</v>
+        <v>-0.360934</v>
       </c>
     </row>
     <row r="30">
@@ -1083,13 +1083,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.018514</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.007337</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.009005000000000001</v>
       </c>
       <c r="E34" s="3" t="n">
         <v>0</v>
@@ -1121,13 +1121,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.018514</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.007337</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.009005000000000001</v>
       </c>
       <c r="E36" s="3" t="n">
         <v>0</v>
@@ -1349,13 +1349,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.118718</v>
+        <v>0.100204</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.112705</v>
+        <v>0.105368</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.08454200000000001</v>
+        <v>0.07553700000000001</v>
       </c>
       <c r="E48" s="3" t="n">
         <v>0.076319</v>
@@ -3146,7 +3146,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" s="5" t="n">
@@ -5674,7 +5674,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -5810,7 +5810,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E80" s="5" t="n">
@@ -6228,7 +6228,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">

--- a/output/pdf_financials_xlsx/LION.xlsx
+++ b/output/pdf_financials_xlsx/LION.xlsx
@@ -2354,16 +2354,16 @@
         </is>
       </c>
       <c r="B101" s="3" t="n">
-        <v>-0.009587999999999999</v>
+        <v>-0.02009</v>
       </c>
       <c r="C101" s="3" t="n">
-        <v>-0.021267</v>
+        <v>-0.034831</v>
       </c>
       <c r="D101" s="3" t="n">
-        <v>0.020375</v>
+        <v>0.015064</v>
       </c>
       <c r="E101" s="3" t="n">
-        <v>-0.000992</v>
+        <v>-0.009882</v>
       </c>
     </row>
     <row r="102">
@@ -2449,16 +2449,16 @@
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>-0.078143</v>
+        <v>-0.088645</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>0.073397</v>
+        <v>0.059833</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>0.0557</v>
+        <v>0.050389</v>
       </c>
       <c r="E106" s="3" t="n">
-        <v>0.061321</v>
+        <v>0.052431</v>
       </c>
     </row>
     <row r="107">
@@ -4408,7 +4408,11 @@
           <t>GST recoverable</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr"/>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E40" s="5" t="n">
         <v>-0.010502</v>
       </c>
